--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -2381,7 +2381,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113551442</v>
+        <v>113551369</v>
       </c>
       <c r="B15" t="n">
         <v>97402</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2433,14 +2433,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fiskraken (S) (knärot), Vstm</t>
+          <t>Fiskrakenskogen  (SV) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563507</v>
+        <v>563322</v>
       </c>
       <c r="R15" t="n">
-        <v>6624502</v>
+        <v>6624545</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>u-Sur-0577</t>
+          <t>U-Sur-0576</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2509,7 +2509,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113551369</v>
+        <v>113551442</v>
       </c>
       <c r="B16" t="n">
         <v>97402</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2561,14 +2561,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskrakenskogen  (SV) (knärot), Vstm</t>
+          <t>Fiskraken (S) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563322</v>
+        <v>563507</v>
       </c>
       <c r="R16" t="n">
-        <v>6624545</v>
+        <v>6624502</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>U-Sur-0576</t>
+          <t>u-Sur-0577</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,10 +10254,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B76" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R76" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,10 +10387,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B77" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R77" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,7 +10254,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B76" t="n">
         <v>98081</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R76" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,7 +10387,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B77" t="n">
         <v>98081</v>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R77" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10257,7 +10257,7 @@
         <v>121290063</v>
       </c>
       <c r="B76" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>121291351</v>
       </c>
       <c r="B77" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,10 +10254,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B76" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R76" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,10 +10387,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B77" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R77" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10257,7 +10257,7 @@
         <v>121291351</v>
       </c>
       <c r="B76" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>121290063</v>
       </c>
       <c r="B77" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,7 +10254,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B76" t="n">
         <v>98098</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R76" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,7 +10387,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B77" t="n">
         <v>98098</v>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R77" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,10 +10254,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B76" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R76" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,10 +10387,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B77" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R77" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10257,7 +10257,7 @@
         <v>121291351</v>
       </c>
       <c r="B76" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>121290063</v>
       </c>
       <c r="B77" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,7 +10254,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B76" t="n">
         <v>98105</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R76" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,7 +10387,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B77" t="n">
         <v>98105</v>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R77" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,7 +10254,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B76" t="n">
         <v>98105</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R76" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,7 +10387,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B77" t="n">
         <v>98105</v>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R77" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10254,10 +10254,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121290063</v>
+        <v>121291351</v>
       </c>
       <c r="B76" t="n">
-        <v>98105</v>
+        <v>98110</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10306,17 +10306,17 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563415</v>
+        <v>563447</v>
       </c>
       <c r="R76" t="n">
-        <v>6624521</v>
+        <v>6624479</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>U-Sur-0799</t>
+          <t>U-Sur-0533</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>foto OK</t>
+          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -10387,10 +10387,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121291351</v>
+        <v>121290063</v>
       </c>
       <c r="B77" t="n">
-        <v>98105</v>
+        <v>98110</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10439,17 +10439,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563447</v>
+        <v>563415</v>
       </c>
       <c r="R77" t="n">
-        <v>6624479</v>
+        <v>6624521</v>
       </c>
       <c r="S77" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>U-Sur-0533</t>
+          <t>U-Sur-0799</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10518,6 +10518,571 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122485434</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98240</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Syd Fiskkraken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>563429</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6624616</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122485428</v>
+      </c>
+      <c r="B79" t="n">
+        <v>90605</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Syd Fiskkraken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>563459</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6624572</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122485424</v>
+      </c>
+      <c r="B80" t="n">
+        <v>90833</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Syd Fiskkraken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>563482</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6624454</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122485433</v>
+      </c>
+      <c r="B81" t="n">
+        <v>105346</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Syd Fiskkraken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>563393</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6624475</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122485432</v>
+      </c>
+      <c r="B82" t="n">
+        <v>95786</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>53</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Syd Fiskkraken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>563279</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6624575</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Liggande murken tallstam</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485434</v>
+        <v>122485428</v>
       </c>
       <c r="B78" t="n">
-        <v>98240</v>
+        <v>90605</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563429</v>
+        <v>563459</v>
       </c>
       <c r="R78" t="n">
-        <v>6624616</v>
+        <v>6624572</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485428</v>
+        <v>122485424</v>
       </c>
       <c r="B79" t="n">
-        <v>90605</v>
+        <v>90833</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10643,25 +10643,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563459</v>
+        <v>563482</v>
       </c>
       <c r="R79" t="n">
-        <v>6624572</v>
+        <v>6624454</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10720,7 +10720,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10742,10 +10747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485424</v>
+        <v>122485433</v>
       </c>
       <c r="B80" t="n">
-        <v>90833</v>
+        <v>105346</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10754,25 +10759,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10782,10 +10787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563482</v>
+        <v>563393</v>
       </c>
       <c r="R80" t="n">
-        <v>6624454</v>
+        <v>6624475</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10831,12 +10836,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485433</v>
+        <v>122485434</v>
       </c>
       <c r="B81" t="n">
-        <v>105346</v>
+        <v>98240</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10870,25 +10870,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563393</v>
+        <v>563429</v>
       </c>
       <c r="R81" t="n">
-        <v>6624475</v>
+        <v>6624616</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485428</v>
+        <v>122485424</v>
       </c>
       <c r="B78" t="n">
-        <v>90605</v>
+        <v>90834</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563459</v>
+        <v>563482</v>
       </c>
       <c r="R78" t="n">
-        <v>6624572</v>
+        <v>6624454</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,7 +10609,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10631,10 +10636,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485424</v>
+        <v>122485432</v>
       </c>
       <c r="B79" t="n">
-        <v>90833</v>
+        <v>95787</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10647,21 +10652,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10671,10 +10676,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563482</v>
+        <v>563279</v>
       </c>
       <c r="R79" t="n">
-        <v>6624454</v>
+        <v>6624575</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10720,12 +10725,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10750,7 +10755,7 @@
         <v>122485433</v>
       </c>
       <c r="B80" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10858,10 +10863,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485434</v>
+        <v>122485428</v>
       </c>
       <c r="B81" t="n">
-        <v>98240</v>
+        <v>90606</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10870,25 +10875,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10898,10 +10903,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563429</v>
+        <v>563459</v>
       </c>
       <c r="R81" t="n">
-        <v>6624616</v>
+        <v>6624572</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10947,7 +10952,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10969,10 +10974,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122485432</v>
+        <v>122485434</v>
       </c>
       <c r="B82" t="n">
-        <v>95786</v>
+        <v>98241</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10981,25 +10986,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11009,10 +11014,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563279</v>
+        <v>563429</v>
       </c>
       <c r="R82" t="n">
-        <v>6624575</v>
+        <v>6624616</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -11058,12 +11063,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485424</v>
+        <v>122485432</v>
       </c>
       <c r="B78" t="n">
-        <v>90834</v>
+        <v>95787</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10536,21 +10536,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563482</v>
+        <v>563279</v>
       </c>
       <c r="R78" t="n">
-        <v>6624454</v>
+        <v>6624575</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,12 +10609,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10636,10 +10636,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485432</v>
+        <v>122485424</v>
       </c>
       <c r="B79" t="n">
-        <v>95787</v>
+        <v>90834</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10652,21 +10652,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10676,10 +10676,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563279</v>
+        <v>563482</v>
       </c>
       <c r="R79" t="n">
-        <v>6624575</v>
+        <v>6624454</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
+          <t>Barrblandskog, fuktsänka</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Liggande murken tallstam</t>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485432</v>
+        <v>122485433</v>
       </c>
       <c r="B78" t="n">
-        <v>95787</v>
+        <v>105350</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563279</v>
+        <v>563393</v>
       </c>
       <c r="R78" t="n">
-        <v>6624575</v>
+        <v>6624475</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,12 +10609,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10636,10 +10631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485424</v>
+        <v>122485432</v>
       </c>
       <c r="B79" t="n">
-        <v>90834</v>
+        <v>95790</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10652,21 +10647,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10676,10 +10671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563482</v>
+        <v>563279</v>
       </c>
       <c r="R79" t="n">
-        <v>6624454</v>
+        <v>6624575</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10725,12 +10720,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10752,10 +10747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485433</v>
+        <v>122485434</v>
       </c>
       <c r="B80" t="n">
-        <v>105347</v>
+        <v>98244</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10764,25 +10759,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10792,10 +10787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563393</v>
+        <v>563429</v>
       </c>
       <c r="R80" t="n">
-        <v>6624475</v>
+        <v>6624616</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10841,7 +10836,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10866,7 +10861,7 @@
         <v>122485428</v>
       </c>
       <c r="B81" t="n">
-        <v>90606</v>
+        <v>90609</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10974,10 +10969,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122485434</v>
+        <v>122485424</v>
       </c>
       <c r="B82" t="n">
-        <v>98241</v>
+        <v>90837</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10986,25 +10981,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11014,10 +11009,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563429</v>
+        <v>563482</v>
       </c>
       <c r="R82" t="n">
-        <v>6624616</v>
+        <v>6624454</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -11063,7 +11058,12 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485433</v>
+        <v>122485432</v>
       </c>
       <c r="B78" t="n">
-        <v>105350</v>
+        <v>95790</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563393</v>
+        <v>563279</v>
       </c>
       <c r="R78" t="n">
-        <v>6624475</v>
+        <v>6624575</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,7 +10609,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10631,10 +10636,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485432</v>
+        <v>122485434</v>
       </c>
       <c r="B79" t="n">
-        <v>95790</v>
+        <v>98244</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10643,25 +10648,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10671,10 +10676,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563279</v>
+        <v>563429</v>
       </c>
       <c r="R79" t="n">
-        <v>6624575</v>
+        <v>6624616</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10720,12 +10725,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10747,10 +10747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485434</v>
+        <v>122485433</v>
       </c>
       <c r="B80" t="n">
-        <v>98244</v>
+        <v>105350</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10759,25 +10759,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563429</v>
+        <v>563393</v>
       </c>
       <c r="R80" t="n">
-        <v>6624616</v>
+        <v>6624475</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485432</v>
+        <v>122485434</v>
       </c>
       <c r="B78" t="n">
-        <v>95790</v>
+        <v>98244</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563279</v>
+        <v>563429</v>
       </c>
       <c r="R78" t="n">
-        <v>6624575</v>
+        <v>6624616</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,12 +10609,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10636,10 +10631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485434</v>
+        <v>122485432</v>
       </c>
       <c r="B79" t="n">
-        <v>98244</v>
+        <v>95790</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10648,25 +10643,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10676,10 +10671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563429</v>
+        <v>563279</v>
       </c>
       <c r="R79" t="n">
-        <v>6624616</v>
+        <v>6624575</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10725,7 +10720,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485434</v>
+        <v>122485428</v>
       </c>
       <c r="B78" t="n">
-        <v>98244</v>
+        <v>90712</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563429</v>
+        <v>563459</v>
       </c>
       <c r="R78" t="n">
-        <v>6624616</v>
+        <v>6624572</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10634,7 +10634,7 @@
         <v>122485432</v>
       </c>
       <c r="B79" t="n">
-        <v>95790</v>
+        <v>95893</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10747,10 +10747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485433</v>
+        <v>122485434</v>
       </c>
       <c r="B80" t="n">
-        <v>105350</v>
+        <v>98347</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10759,25 +10759,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563393</v>
+        <v>563429</v>
       </c>
       <c r="R80" t="n">
-        <v>6624475</v>
+        <v>6624616</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485428</v>
+        <v>122485433</v>
       </c>
       <c r="B81" t="n">
-        <v>90609</v>
+        <v>105453</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10874,21 +10874,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3215</v>
+        <v>221144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563459</v>
+        <v>563393</v>
       </c>
       <c r="R81" t="n">
-        <v>6624572</v>
+        <v>6624475</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10972,7 +10972,7 @@
         <v>122485424</v>
       </c>
       <c r="B82" t="n">
-        <v>90837</v>
+        <v>90940</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485428</v>
+        <v>122485433</v>
       </c>
       <c r="B78" t="n">
-        <v>90712</v>
+        <v>105461</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10536,21 +10536,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3215</v>
+        <v>221144</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563459</v>
+        <v>563393</v>
       </c>
       <c r="R78" t="n">
-        <v>6624572</v>
+        <v>6624475</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10634,7 +10634,7 @@
         <v>122485432</v>
       </c>
       <c r="B79" t="n">
-        <v>95893</v>
+        <v>95901</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>122485434</v>
       </c>
       <c r="B80" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10858,10 +10858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485433</v>
+        <v>122485424</v>
       </c>
       <c r="B81" t="n">
-        <v>105453</v>
+        <v>90944</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10870,25 +10870,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563393</v>
+        <v>563482</v>
       </c>
       <c r="R81" t="n">
-        <v>6624475</v>
+        <v>6624454</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10947,7 +10947,12 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10969,10 +10974,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122485424</v>
+        <v>122485428</v>
       </c>
       <c r="B82" t="n">
-        <v>90940</v>
+        <v>90716</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10981,25 +10986,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11009,10 +11014,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563482</v>
+        <v>563459</v>
       </c>
       <c r="R82" t="n">
-        <v>6624454</v>
+        <v>6624572</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -11058,12 +11063,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10631,10 +10631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485432</v>
+        <v>122485434</v>
       </c>
       <c r="B79" t="n">
-        <v>95901</v>
+        <v>98355</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10643,25 +10643,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563279</v>
+        <v>563429</v>
       </c>
       <c r="R79" t="n">
-        <v>6624575</v>
+        <v>6624616</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10720,12 +10720,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10747,10 +10742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485434</v>
+        <v>122485424</v>
       </c>
       <c r="B80" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10759,25 +10754,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10787,10 +10782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563429</v>
+        <v>563482</v>
       </c>
       <c r="R80" t="n">
-        <v>6624616</v>
+        <v>6624454</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10836,7 +10831,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485424</v>
+        <v>122485432</v>
       </c>
       <c r="B81" t="n">
-        <v>90944</v>
+        <v>95901</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10874,21 +10874,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563482</v>
+        <v>563279</v>
       </c>
       <c r="R81" t="n">
-        <v>6624454</v>
+        <v>6624575</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10947,12 +10947,12 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485433</v>
+        <v>122485424</v>
       </c>
       <c r="B78" t="n">
-        <v>105461</v>
+        <v>90944</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563393</v>
+        <v>563482</v>
       </c>
       <c r="R78" t="n">
-        <v>6624475</v>
+        <v>6624454</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,7 +10609,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10631,10 +10636,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485434</v>
+        <v>122485428</v>
       </c>
       <c r="B79" t="n">
-        <v>98355</v>
+        <v>90716</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10643,25 +10648,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10671,10 +10676,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563429</v>
+        <v>563459</v>
       </c>
       <c r="R79" t="n">
-        <v>6624616</v>
+        <v>6624572</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10720,7 +10725,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10742,10 +10747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485424</v>
+        <v>122485432</v>
       </c>
       <c r="B80" t="n">
-        <v>90944</v>
+        <v>95903</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10758,21 +10763,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10782,10 +10787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563482</v>
+        <v>563279</v>
       </c>
       <c r="R80" t="n">
-        <v>6624454</v>
+        <v>6624575</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10831,12 +10836,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10858,10 +10863,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485432</v>
+        <v>122485433</v>
       </c>
       <c r="B81" t="n">
-        <v>95901</v>
+        <v>105463</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10870,25 +10875,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10898,10 +10903,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563279</v>
+        <v>563393</v>
       </c>
       <c r="R81" t="n">
-        <v>6624575</v>
+        <v>6624475</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10947,12 +10952,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122485428</v>
+        <v>122485434</v>
       </c>
       <c r="B82" t="n">
-        <v>90716</v>
+        <v>98357</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10986,25 +10986,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563459</v>
+        <v>563429</v>
       </c>
       <c r="R82" t="n">
-        <v>6624572</v>
+        <v>6624616</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485424</v>
+        <v>122485433</v>
       </c>
       <c r="B78" t="n">
-        <v>90944</v>
+        <v>105463</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563482</v>
+        <v>563393</v>
       </c>
       <c r="R78" t="n">
-        <v>6624454</v>
+        <v>6624475</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,12 +10609,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10636,10 +10631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485428</v>
+        <v>122485434</v>
       </c>
       <c r="B79" t="n">
-        <v>90716</v>
+        <v>98357</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10648,25 +10643,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10676,10 +10671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563459</v>
+        <v>563429</v>
       </c>
       <c r="R79" t="n">
-        <v>6624572</v>
+        <v>6624616</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10725,7 +10720,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10747,10 +10742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485432</v>
+        <v>122485428</v>
       </c>
       <c r="B80" t="n">
-        <v>95903</v>
+        <v>90716</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10759,25 +10754,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10787,10 +10782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563279</v>
+        <v>563459</v>
       </c>
       <c r="R80" t="n">
-        <v>6624575</v>
+        <v>6624572</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10836,12 +10831,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10863,10 +10853,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485433</v>
+        <v>122485424</v>
       </c>
       <c r="B81" t="n">
-        <v>105463</v>
+        <v>90944</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10875,25 +10865,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10903,10 +10893,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563393</v>
+        <v>563482</v>
       </c>
       <c r="R81" t="n">
-        <v>6624475</v>
+        <v>6624454</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10952,7 +10942,12 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10974,10 +10969,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122485434</v>
+        <v>122485432</v>
       </c>
       <c r="B82" t="n">
-        <v>98357</v>
+        <v>95903</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10986,25 +10981,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11014,10 +11009,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563429</v>
+        <v>563279</v>
       </c>
       <c r="R82" t="n">
-        <v>6624616</v>
+        <v>6624575</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -11063,7 +11058,12 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11083,6 +11083,359 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>123093296</v>
+      </c>
+      <c r="B83" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fiskkraken S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>563612</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6624481</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>123093244</v>
+      </c>
+      <c r="B84" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Fiskkraken S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>563463</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6624447</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>123093272</v>
+      </c>
+      <c r="B85" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fiskkraken S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>563490</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6624468</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485433</v>
+        <v>122485424</v>
       </c>
       <c r="B78" t="n">
-        <v>105463</v>
+        <v>90952</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563393</v>
+        <v>563482</v>
       </c>
       <c r="R78" t="n">
-        <v>6624475</v>
+        <v>6624454</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,7 +10609,12 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10631,10 +10636,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485434</v>
+        <v>122485428</v>
       </c>
       <c r="B79" t="n">
-        <v>98357</v>
+        <v>90724</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10643,25 +10648,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10671,10 +10676,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563429</v>
+        <v>563459</v>
       </c>
       <c r="R79" t="n">
-        <v>6624616</v>
+        <v>6624572</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10720,7 +10725,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10742,10 +10747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485428</v>
+        <v>122485434</v>
       </c>
       <c r="B80" t="n">
-        <v>90716</v>
+        <v>98365</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10754,25 +10759,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10782,10 +10787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563459</v>
+        <v>563429</v>
       </c>
       <c r="R80" t="n">
-        <v>6624572</v>
+        <v>6624616</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10831,7 +10836,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10853,10 +10858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485424</v>
+        <v>122485432</v>
       </c>
       <c r="B81" t="n">
-        <v>90944</v>
+        <v>95911</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10869,21 +10874,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10893,10 +10898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563482</v>
+        <v>563279</v>
       </c>
       <c r="R81" t="n">
-        <v>6624454</v>
+        <v>6624575</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10942,12 +10947,12 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Liggande granstam</t>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10969,10 +10974,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122485432</v>
+        <v>122485433</v>
       </c>
       <c r="B82" t="n">
-        <v>95903</v>
+        <v>105471</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10981,25 +10986,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11009,10 +11014,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563279</v>
+        <v>563393</v>
       </c>
       <c r="R82" t="n">
-        <v>6624575</v>
+        <v>6624475</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -11058,12 +11063,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11085,10 +11085,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123093296</v>
+        <v>123093272</v>
       </c>
       <c r="B83" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563612</v>
+        <v>563490</v>
       </c>
       <c r="R83" t="n">
-        <v>6624481</v>
+        <v>6624468</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11164,11 +11164,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11206,10 +11201,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123093244</v>
+        <v>123093296</v>
       </c>
       <c r="B84" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11249,10 +11244,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563463</v>
+        <v>563612</v>
       </c>
       <c r="R84" t="n">
-        <v>6624447</v>
+        <v>6624481</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11285,6 +11280,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11322,10 +11322,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093272</v>
+        <v>123093244</v>
       </c>
       <c r="B85" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11365,10 +11365,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563490</v>
+        <v>563463</v>
       </c>
       <c r="R85" t="n">
-        <v>6624468</v>
+        <v>6624447</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10520,10 +10520,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485424</v>
+        <v>122485434</v>
       </c>
       <c r="B78" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,25 +10532,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563482</v>
+        <v>563429</v>
       </c>
       <c r="R78" t="n">
-        <v>6624454</v>
+        <v>6624616</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10609,12 +10609,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10747,10 +10742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485434</v>
+        <v>122485424</v>
       </c>
       <c r="B80" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10759,25 +10754,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10787,10 +10782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563429</v>
+        <v>563482</v>
       </c>
       <c r="R80" t="n">
-        <v>6624616</v>
+        <v>6624454</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10836,7 +10831,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123093296</v>
+        <v>123093244</v>
       </c>
       <c r="B84" t="n">
         <v>90952</v>
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563612</v>
+        <v>563463</v>
       </c>
       <c r="R84" t="n">
-        <v>6624481</v>
+        <v>6624447</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11280,11 +11280,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11322,7 +11317,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093244</v>
+        <v>123093296</v>
       </c>
       <c r="B85" t="n">
         <v>90952</v>
@@ -11365,10 +11360,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563463</v>
+        <v>563612</v>
       </c>
       <c r="R85" t="n">
-        <v>6624447</v>
+        <v>6624481</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11401,6 +11396,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10631,10 +10631,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485428</v>
+        <v>122485432</v>
       </c>
       <c r="B79" t="n">
-        <v>90724</v>
+        <v>95911</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10643,25 +10643,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563459</v>
+        <v>563279</v>
       </c>
       <c r="R79" t="n">
-        <v>6624572</v>
+        <v>6624575</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10720,7 +10720,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Liggande murken tallstam</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10742,10 +10747,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485424</v>
+        <v>122485433</v>
       </c>
       <c r="B80" t="n">
-        <v>90952</v>
+        <v>105471</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10754,25 +10759,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10782,10 +10787,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563482</v>
+        <v>563393</v>
       </c>
       <c r="R80" t="n">
-        <v>6624454</v>
+        <v>6624475</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10831,12 +10836,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Barrblandskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122485432</v>
+        <v>122485428</v>
       </c>
       <c r="B81" t="n">
-        <v>95911</v>
+        <v>90724</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10870,25 +10870,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563279</v>
+        <v>563459</v>
       </c>
       <c r="R81" t="n">
-        <v>6624575</v>
+        <v>6624572</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10947,12 +10947,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10974,10 +10969,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122485433</v>
+        <v>122485424</v>
       </c>
       <c r="B82" t="n">
-        <v>105471</v>
+        <v>90952</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10986,25 +10981,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11014,10 +11009,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563393</v>
+        <v>563482</v>
       </c>
       <c r="R82" t="n">
-        <v>6624475</v>
+        <v>6624454</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -11063,7 +11058,12 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123093272</v>
+        <v>123093244</v>
       </c>
       <c r="B83" t="n">
         <v>90952</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563490</v>
+        <v>563463</v>
       </c>
       <c r="R83" t="n">
-        <v>6624468</v>
+        <v>6624447</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11201,7 +11201,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123093244</v>
+        <v>123093296</v>
       </c>
       <c r="B84" t="n">
         <v>90952</v>
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563463</v>
+        <v>563612</v>
       </c>
       <c r="R84" t="n">
-        <v>6624447</v>
+        <v>6624481</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11280,6 +11280,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11317,7 +11322,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093296</v>
+        <v>123093272</v>
       </c>
       <c r="B85" t="n">
         <v>90952</v>
@@ -11360,10 +11365,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563612</v>
+        <v>563490</v>
       </c>
       <c r="R85" t="n">
-        <v>6624481</v>
+        <v>6624468</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11396,11 +11401,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11085,7 +11085,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123093244</v>
+        <v>123093296</v>
       </c>
       <c r="B83" t="n">
         <v>90952</v>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563463</v>
+        <v>563612</v>
       </c>
       <c r="R83" t="n">
-        <v>6624447</v>
+        <v>6624481</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11164,6 +11164,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11201,7 +11206,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123093296</v>
+        <v>123093244</v>
       </c>
       <c r="B84" t="n">
         <v>90952</v>
@@ -11244,10 +11249,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563612</v>
+        <v>563463</v>
       </c>
       <c r="R84" t="n">
-        <v>6624481</v>
+        <v>6624447</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11280,11 +11285,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11085,10 +11085,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123093296</v>
+        <v>123093244</v>
       </c>
       <c r="B83" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563612</v>
+        <v>563463</v>
       </c>
       <c r="R83" t="n">
-        <v>6624481</v>
+        <v>6624447</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11164,11 +11164,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11206,10 +11201,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123093244</v>
+        <v>123093272</v>
       </c>
       <c r="B84" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11249,10 +11244,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563463</v>
+        <v>563490</v>
       </c>
       <c r="R84" t="n">
-        <v>6624447</v>
+        <v>6624468</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11322,10 +11317,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093272</v>
+        <v>123093296</v>
       </c>
       <c r="B85" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11365,10 +11360,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563490</v>
+        <v>563612</v>
       </c>
       <c r="R85" t="n">
-        <v>6624468</v>
+        <v>6624481</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11401,6 +11396,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11085,10 +11085,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123093244</v>
+        <v>123093296</v>
       </c>
       <c r="B83" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563463</v>
+        <v>563612</v>
       </c>
       <c r="R83" t="n">
-        <v>6624447</v>
+        <v>6624481</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11164,6 +11164,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11201,10 +11206,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123093272</v>
+        <v>123093244</v>
       </c>
       <c r="B84" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11244,10 +11249,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563490</v>
+        <v>563463</v>
       </c>
       <c r="R84" t="n">
-        <v>6624468</v>
+        <v>6624447</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11317,10 +11322,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093296</v>
+        <v>123093272</v>
       </c>
       <c r="B85" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11360,10 +11365,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563612</v>
+        <v>563490</v>
       </c>
       <c r="R85" t="n">
-        <v>6624481</v>
+        <v>6624468</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11396,11 +11401,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11088,7 +11088,7 @@
         <v>123093296</v>
       </c>
       <c r="B83" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11206,10 +11206,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123093244</v>
+        <v>123093272</v>
       </c>
       <c r="B84" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563463</v>
+        <v>563490</v>
       </c>
       <c r="R84" t="n">
-        <v>6624447</v>
+        <v>6624468</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11322,10 +11322,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093272</v>
+        <v>123093244</v>
       </c>
       <c r="B85" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11365,10 +11365,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563490</v>
+        <v>563463</v>
       </c>
       <c r="R85" t="n">
-        <v>6624468</v>
+        <v>6624447</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11085,10 +11085,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123093296</v>
+        <v>123093244</v>
       </c>
       <c r="B83" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563612</v>
+        <v>563463</v>
       </c>
       <c r="R83" t="n">
-        <v>6624481</v>
+        <v>6624447</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11164,11 +11164,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11209,7 +11204,7 @@
         <v>123093272</v>
       </c>
       <c r="B84" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11322,10 +11317,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093244</v>
+        <v>123093296</v>
       </c>
       <c r="B85" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11365,10 +11360,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563463</v>
+        <v>563612</v>
       </c>
       <c r="R85" t="n">
-        <v>6624447</v>
+        <v>6624481</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11401,6 +11396,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11085,10 +11085,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123093244</v>
+        <v>123093296</v>
       </c>
       <c r="B83" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563463</v>
+        <v>563612</v>
       </c>
       <c r="R83" t="n">
-        <v>6624447</v>
+        <v>6624481</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11164,6 +11164,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11204,7 +11209,7 @@
         <v>123093272</v>
       </c>
       <c r="B84" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11317,10 +11322,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123093296</v>
+        <v>123093244</v>
       </c>
       <c r="B85" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11360,10 +11365,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563612</v>
+        <v>563463</v>
       </c>
       <c r="R85" t="n">
-        <v>6624481</v>
+        <v>6624447</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11396,11 +11401,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,7 +2253,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113436752</v>
+        <v>115332800</v>
       </c>
       <c r="B14" t="n">
         <v>97650</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2302,17 +2302,21 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fiskrakenskogen (2) (knärot), Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563544</v>
+        <v>563546</v>
       </c>
       <c r="R14" t="n">
-        <v>6624579</v>
+        <v>6624433</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2337,19 +2341,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>U-Sur-0546</t>
-        </is>
-      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,23 +2364,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113551442</v>
+        <v>115332530</v>
       </c>
       <c r="B15" t="n">
         <v>97650</v>
@@ -2416,7 +2411,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2430,20 +2425,24 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fiskraken (S) (knärot), Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563507</v>
+        <v>563512</v>
       </c>
       <c r="R15" t="n">
-        <v>6624502</v>
+        <v>6624412</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2465,19 +2464,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>u-Sur-0577</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2493,23 +2497,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113551369</v>
+        <v>115331339</v>
       </c>
       <c r="B16" t="n">
         <v>97650</v>
@@ -2558,20 +2558,24 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskrakenskogen  (SV) (knärot), Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563322</v>
+        <v>563492</v>
       </c>
       <c r="R16" t="n">
-        <v>6624545</v>
+        <v>6624444</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2593,19 +2597,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>U-Sur-0576</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2621,23 +2630,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115332800</v>
+        <v>115452935</v>
       </c>
       <c r="B17" t="n">
         <v>97650</v>
@@ -2672,7 +2677,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2686,21 +2691,17 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrkenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563546</v>
+        <v>563614</v>
       </c>
       <c r="R17" t="n">
-        <v>6624433</v>
+        <v>6624509</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2727,12 +2728,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2748,22 +2759,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115332530</v>
+        <v>115452717</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
+        <v>104737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2772,30 +2783,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2809,21 +2820,17 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563512</v>
+        <v>563606</v>
       </c>
       <c r="R18" t="n">
-        <v>6624412</v>
+        <v>6624632</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2850,22 +2857,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,19 +2888,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115331339</v>
+        <v>115452851</v>
       </c>
       <c r="B19" t="n">
         <v>97650</v>
@@ -2942,24 +2949,20 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563492</v>
+        <v>563600</v>
       </c>
       <c r="R19" t="n">
-        <v>6624444</v>
+        <v>6624606</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2983,22 +2986,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3014,22 +3017,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115452935</v>
+        <v>115452883</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
+        <v>104737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3038,35 +3041,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3078,14 +3081,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fiskkrkenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563614</v>
+        <v>563617</v>
       </c>
       <c r="R20" t="n">
-        <v>6624509</v>
+        <v>6624585</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3155,10 +3158,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115452717</v>
+        <v>115452914</v>
       </c>
       <c r="B21" t="n">
-        <v>104737</v>
+        <v>97650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3167,30 +3170,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3211,10 +3214,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563606</v>
+        <v>563623</v>
       </c>
       <c r="R21" t="n">
-        <v>6624632</v>
+        <v>6624566</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3284,66 +3287,58 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115452851</v>
+        <v>115440622</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
+        <v>57281</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563600</v>
+        <v>563578</v>
       </c>
       <c r="R22" t="n">
-        <v>6624606</v>
+        <v>6624436</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3375,7 +3370,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3385,7 +3380,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3394,26 +3394,30 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115452883</v>
+        <v>115602430</v>
       </c>
       <c r="B23" t="n">
         <v>104737</v>
@@ -3448,7 +3452,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3456,26 +3460,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>av Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563617</v>
+        <v>563476</v>
       </c>
       <c r="R23" t="n">
-        <v>6624585</v>
+        <v>6624515</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3499,22 +3500,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3530,22 +3521,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115452914</v>
+        <v>116057705</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
+        <v>97659</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3577,7 +3568,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3598,10 +3589,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563623</v>
+        <v>563515</v>
       </c>
       <c r="R24" t="n">
-        <v>6624566</v>
+        <v>6624433</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3628,22 +3619,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3664,17 +3655,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115529573</v>
+        <v>116057717</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
+        <v>97659</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3706,7 +3697,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3723,17 +3714,17 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skallmossarna SO, 2 (knärot), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563524</v>
+        <v>563550</v>
       </c>
       <c r="R25" t="n">
-        <v>6624421</v>
+        <v>6624428</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3755,19 +3746,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>U-Sur-0532</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3783,74 +3779,78 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115440622</v>
+        <v>116057037</v>
       </c>
       <c r="B26" t="n">
-        <v>57281</v>
+        <v>97659</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563578</v>
+        <v>563502</v>
       </c>
       <c r="R26" t="n">
-        <v>6624436</v>
+        <v>6624626</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3877,27 +3877,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3906,33 +3901,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115602430</v>
+        <v>116057566</v>
       </c>
       <c r="B27" t="n">
-        <v>104737</v>
+        <v>104746</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3964,31 +3955,34 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>av Fiskkraken, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563476</v>
+        <v>563424</v>
       </c>
       <c r="R27" t="n">
-        <v>6624515</v>
+        <v>6624463</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4012,12 +4006,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4033,19 +4037,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116057705</v>
+        <v>116057720</v>
       </c>
       <c r="B28" t="n">
         <v>97659</v>
@@ -4080,7 +4084,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4101,10 +4105,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563515</v>
+        <v>563561</v>
       </c>
       <c r="R28" t="n">
-        <v>6624433</v>
+        <v>6624427</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4174,10 +4178,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116057717</v>
+        <v>116042256</v>
       </c>
       <c r="B29" t="n">
-        <v>97659</v>
+        <v>96622</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4186,30 +4190,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4217,26 +4221,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563550</v>
+        <v>563537</v>
       </c>
       <c r="R29" t="n">
-        <v>6624428</v>
+        <v>6624625</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4265,7 +4269,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4275,7 +4279,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4288,22 +4292,27 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116057037</v>
+        <v>116057150</v>
       </c>
       <c r="B30" t="n">
         <v>97659</v>
@@ -4338,7 +4347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4359,10 +4368,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563502</v>
+        <v>563458</v>
       </c>
       <c r="R30" t="n">
-        <v>6624626</v>
+        <v>6624624</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4432,10 +4441,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116057566</v>
+        <v>116057372</v>
       </c>
       <c r="B31" t="n">
-        <v>104746</v>
+        <v>97659</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4444,30 +4453,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4488,10 +4497,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563424</v>
+        <v>563441</v>
       </c>
       <c r="R31" t="n">
-        <v>6624463</v>
+        <v>6624477</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4561,7 +4570,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116057720</v>
+        <v>116057204</v>
       </c>
       <c r="B32" t="n">
         <v>97659</v>
@@ -4596,7 +4605,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4617,10 +4626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563561</v>
+        <v>563459</v>
       </c>
       <c r="R32" t="n">
-        <v>6624427</v>
+        <v>6624536</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4683,17 +4692,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116042256</v>
+        <v>116057108</v>
       </c>
       <c r="B33" t="n">
-        <v>96622</v>
+        <v>97659</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4702,30 +4711,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4733,26 +4742,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563537</v>
+        <v>563438</v>
       </c>
       <c r="R33" t="n">
-        <v>6624625</v>
+        <v>6624576</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4781,7 +4790,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4791,7 +4800,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4804,30 +4813,25 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116057150</v>
+        <v>116042390</v>
       </c>
       <c r="B34" t="n">
-        <v>97659</v>
+        <v>96622</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4836,30 +4840,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4867,23 +4871,16 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563458</v>
+        <v>563417</v>
       </c>
       <c r="R34" t="n">
-        <v>6624624</v>
+        <v>6624534</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4915,7 +4912,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4925,7 +4922,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4934,26 +4931,30 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116057372</v>
+        <v>116057189</v>
       </c>
       <c r="B35" t="n">
         <v>97659</v>
@@ -4988,7 +4989,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5009,10 +5010,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563441</v>
+        <v>563435</v>
       </c>
       <c r="R35" t="n">
-        <v>6624477</v>
+        <v>6624509</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5082,7 +5083,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116057204</v>
+        <v>116057331</v>
       </c>
       <c r="B36" t="n">
         <v>97659</v>
@@ -5117,7 +5118,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5138,10 +5139,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563459</v>
+        <v>563434</v>
       </c>
       <c r="R36" t="n">
-        <v>6624536</v>
+        <v>6624484</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5211,7 +5212,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116057108</v>
+        <v>116057635</v>
       </c>
       <c r="B37" t="n">
         <v>97659</v>
@@ -5246,7 +5247,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5267,10 +5268,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563438</v>
+        <v>563401</v>
       </c>
       <c r="R37" t="n">
-        <v>6624576</v>
+        <v>6624447</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5340,10 +5341,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116042390</v>
+        <v>116057445</v>
       </c>
       <c r="B38" t="n">
-        <v>96622</v>
+        <v>90744</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5356,43 +5357,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221946</v>
+        <v>5420</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563417</v>
+        <v>563447</v>
       </c>
       <c r="R38" t="n">
-        <v>6624534</v>
+        <v>6624478</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5424,7 +5427,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5434,7 +5437,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Invid tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5443,30 +5451,26 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>116057189</v>
+        <v>116057251</v>
       </c>
       <c r="B39" t="n">
         <v>97659</v>
@@ -5501,7 +5505,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5522,10 +5526,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563435</v>
+        <v>563447</v>
       </c>
       <c r="R39" t="n">
-        <v>6624509</v>
+        <v>6624476</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5595,7 +5599,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>116057331</v>
+        <v>116042524</v>
       </c>
       <c r="B40" t="n">
         <v>97659</v>
@@ -5630,7 +5634,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5644,20 +5648,24 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563434</v>
+        <v>563415</v>
       </c>
       <c r="R40" t="n">
-        <v>6624484</v>
+        <v>6624523</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5686,7 +5694,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5696,7 +5704,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5709,22 +5717,31 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>116057635</v>
+        <v>116057713</v>
       </c>
       <c r="B41" t="n">
         <v>97659</v>
@@ -5780,10 +5797,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563401</v>
+        <v>563533</v>
       </c>
       <c r="R41" t="n">
-        <v>6624447</v>
+        <v>6624432</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5846,17 +5863,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>116057445</v>
+        <v>116057764</v>
       </c>
       <c r="B42" t="n">
-        <v>90744</v>
+        <v>97659</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5865,38 +5882,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5904,10 +5926,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563447</v>
+        <v>563560</v>
       </c>
       <c r="R42" t="n">
-        <v>6624478</v>
+        <v>6624441</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5952,11 +5974,6 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Invid tall</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5975,14 +5992,14 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Seppo Ormiskangas, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>116057251</v>
+        <v>116057179</v>
       </c>
       <c r="B43" t="n">
         <v>97659</v>
@@ -6038,10 +6055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563447</v>
+        <v>563430</v>
       </c>
       <c r="R43" t="n">
-        <v>6624476</v>
+        <v>6624513</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6111,7 +6128,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116042524</v>
+        <v>116057008</v>
       </c>
       <c r="B44" t="n">
         <v>97659</v>
@@ -6160,24 +6177,20 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563415</v>
+        <v>563523</v>
       </c>
       <c r="R44" t="n">
-        <v>6624523</v>
+        <v>6624636</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6206,7 +6219,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6216,7 +6229,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6229,31 +6242,22 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116057713</v>
+        <v>116057342</v>
       </c>
       <c r="B45" t="n">
         <v>97659</v>
@@ -6309,10 +6313,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563533</v>
+        <v>563447</v>
       </c>
       <c r="R45" t="n">
-        <v>6624432</v>
+        <v>6624483</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6375,14 +6379,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>116057764</v>
+        <v>116057525</v>
       </c>
       <c r="B46" t="n">
         <v>97659</v>
@@ -6417,7 +6421,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6438,10 +6442,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563560</v>
+        <v>563441</v>
       </c>
       <c r="R46" t="n">
-        <v>6624441</v>
+        <v>6624475</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6504,14 +6508,14 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>116057179</v>
+        <v>116057624</v>
       </c>
       <c r="B47" t="n">
         <v>97659</v>
@@ -6546,7 +6550,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6567,10 +6571,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563430</v>
+        <v>563400</v>
       </c>
       <c r="R47" t="n">
-        <v>6624513</v>
+        <v>6624449</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6640,7 +6644,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116057008</v>
+        <v>116057643</v>
       </c>
       <c r="B48" t="n">
         <v>97659</v>
@@ -6675,7 +6679,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6696,10 +6700,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563523</v>
+        <v>563411</v>
       </c>
       <c r="R48" t="n">
-        <v>6624636</v>
+        <v>6624447</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6769,7 +6773,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116057342</v>
+        <v>116057699</v>
       </c>
       <c r="B49" t="n">
         <v>97659</v>
@@ -6804,7 +6808,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6825,10 +6829,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563447</v>
+        <v>563505</v>
       </c>
       <c r="R49" t="n">
-        <v>6624483</v>
+        <v>6624422</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6891,14 +6895,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>116057525</v>
+        <v>116057176</v>
       </c>
       <c r="B50" t="n">
         <v>97659</v>
@@ -6933,7 +6937,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6954,10 +6958,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>563441</v>
+        <v>563423</v>
       </c>
       <c r="R50" t="n">
-        <v>6624475</v>
+        <v>6624532</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -7027,7 +7031,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116057624</v>
+        <v>116057677</v>
       </c>
       <c r="B51" t="n">
         <v>97659</v>
@@ -7062,7 +7066,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7083,10 +7087,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563400</v>
+        <v>563473</v>
       </c>
       <c r="R51" t="n">
-        <v>6624449</v>
+        <v>6624426</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -7149,14 +7153,14 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116057643</v>
+        <v>116057798</v>
       </c>
       <c r="B52" t="n">
         <v>97659</v>
@@ -7212,10 +7216,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563411</v>
+        <v>563598</v>
       </c>
       <c r="R52" t="n">
-        <v>6624447</v>
+        <v>6624441</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -7285,7 +7289,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116057699</v>
+        <v>116057631</v>
       </c>
       <c r="B53" t="n">
         <v>97659</v>
@@ -7320,7 +7324,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7341,10 +7345,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563505</v>
+        <v>563404</v>
       </c>
       <c r="R53" t="n">
-        <v>6624422</v>
+        <v>6624452</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7407,14 +7411,14 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116057176</v>
+        <v>116057793</v>
       </c>
       <c r="B54" t="n">
         <v>97659</v>
@@ -7449,7 +7453,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7470,10 +7474,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563423</v>
+        <v>563592</v>
       </c>
       <c r="R54" t="n">
-        <v>6624532</v>
+        <v>6624431</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7543,7 +7547,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116057677</v>
+        <v>116057540</v>
       </c>
       <c r="B55" t="n">
         <v>97659</v>
@@ -7578,7 +7582,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7599,10 +7603,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>563473</v>
+        <v>563445</v>
       </c>
       <c r="R55" t="n">
-        <v>6624426</v>
+        <v>6624460</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7665,14 +7669,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116057798</v>
+        <v>116057654</v>
       </c>
       <c r="B56" t="n">
         <v>97659</v>
@@ -7707,7 +7711,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7728,10 +7732,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>563598</v>
+        <v>563458</v>
       </c>
       <c r="R56" t="n">
-        <v>6624441</v>
+        <v>6624424</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7794,14 +7798,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116057631</v>
+        <v>116057016</v>
       </c>
       <c r="B57" t="n">
         <v>97659</v>
@@ -7857,10 +7861,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>563404</v>
+        <v>563522</v>
       </c>
       <c r="R57" t="n">
-        <v>6624452</v>
+        <v>6624629</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7930,10 +7934,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>116057793</v>
+        <v>116057638</v>
       </c>
       <c r="B58" t="n">
-        <v>97659</v>
+        <v>104746</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7942,30 +7946,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7986,10 +7990,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>563592</v>
+        <v>563401</v>
       </c>
       <c r="R58" t="n">
-        <v>6624431</v>
+        <v>6624447</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -8059,7 +8063,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>116057540</v>
+        <v>116057709</v>
       </c>
       <c r="B59" t="n">
         <v>97659</v>
@@ -8094,7 +8098,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8115,10 +8119,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>563445</v>
+        <v>563523</v>
       </c>
       <c r="R59" t="n">
-        <v>6624460</v>
+        <v>6624427</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -8181,17 +8185,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>116057654</v>
+        <v>116042323</v>
       </c>
       <c r="B60" t="n">
-        <v>97659</v>
+        <v>96619</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8200,30 +8204,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8231,26 +8235,22 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563458</v>
+        <v>563420</v>
       </c>
       <c r="R60" t="n">
-        <v>6624424</v>
+        <v>6624535</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8302,25 +8302,30 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>116057016</v>
+        <v>116040948</v>
       </c>
       <c r="B61" t="n">
-        <v>97659</v>
+        <v>96619</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8329,30 +8334,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8360,26 +8365,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563522</v>
+        <v>563537</v>
       </c>
       <c r="R61" t="n">
-        <v>6624629</v>
+        <v>6624625</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8408,7 +8413,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8418,7 +8423,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8431,25 +8436,30 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>116057638</v>
+        <v>116057723</v>
       </c>
       <c r="B62" t="n">
-        <v>104746</v>
+        <v>97659</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8458,30 +8468,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8502,10 +8512,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563401</v>
+        <v>563549</v>
       </c>
       <c r="R62" t="n">
-        <v>6624447</v>
+        <v>6624415</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8568,17 +8578,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>116057709</v>
+        <v>116057573</v>
       </c>
       <c r="B63" t="n">
-        <v>97659</v>
+        <v>104746</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8587,30 +8597,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8631,10 +8641,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563523</v>
+        <v>563415</v>
       </c>
       <c r="R63" t="n">
-        <v>6624427</v>
+        <v>6624457</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8697,17 +8707,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>116042323</v>
+        <v>116057689</v>
       </c>
       <c r="B64" t="n">
-        <v>96619</v>
+        <v>97659</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8716,25 +8726,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -8747,22 +8757,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>563420</v>
+        <v>563486</v>
       </c>
       <c r="R64" t="n">
-        <v>6624535</v>
+        <v>6624438</v>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8791,7 +8805,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8801,7 +8815,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8814,30 +8828,25 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>116040948</v>
+        <v>116057734</v>
       </c>
       <c r="B65" t="n">
-        <v>96619</v>
+        <v>97659</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8846,30 +8855,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8877,26 +8886,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563537</v>
+        <v>563562</v>
       </c>
       <c r="R65" t="n">
-        <v>6624625</v>
+        <v>6624421</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8925,7 +8934,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8935,7 +8944,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8948,27 +8957,22 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>116057723</v>
+        <v>116057553</v>
       </c>
       <c r="B66" t="n">
         <v>97659</v>
@@ -9003,7 +9007,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9024,10 +9028,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563549</v>
+        <v>563424</v>
       </c>
       <c r="R66" t="n">
-        <v>6624415</v>
+        <v>6624468</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -9090,17 +9094,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>116057573</v>
+        <v>116057617</v>
       </c>
       <c r="B67" t="n">
-        <v>104746</v>
+        <v>97659</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9109,30 +9113,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9153,10 +9157,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563415</v>
+        <v>563413</v>
       </c>
       <c r="R67" t="n">
-        <v>6624457</v>
+        <v>6624452</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -9226,7 +9230,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>116057689</v>
+        <v>116057023</v>
       </c>
       <c r="B68" t="n">
         <v>97659</v>
@@ -9261,7 +9265,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9282,10 +9286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>563486</v>
+        <v>563515</v>
       </c>
       <c r="R68" t="n">
-        <v>6624438</v>
+        <v>6624652</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9348,44 +9352,44 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>116057734</v>
+        <v>116057309</v>
       </c>
       <c r="B69" t="n">
-        <v>97659</v>
+        <v>57281</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -9393,17 +9397,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9411,13 +9411,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563562</v>
+        <v>563448</v>
       </c>
       <c r="R69" t="n">
-        <v>6624421</v>
+        <v>6624536</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9465,7 +9465,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9477,62 +9476,58 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>116057553</v>
+        <v>116057771</v>
       </c>
       <c r="B70" t="n">
-        <v>97659</v>
+        <v>57281</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9540,10 +9535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563424</v>
+        <v>563542</v>
       </c>
       <c r="R70" t="n">
-        <v>6624468</v>
+        <v>6624450</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9594,7 +9589,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9613,69 +9607,61 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>116057617</v>
+        <v>116041402</v>
       </c>
       <c r="B71" t="n">
-        <v>97659</v>
+        <v>57281</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>563413</v>
+        <v>563537</v>
       </c>
       <c r="R71" t="n">
-        <v>6624452</v>
+        <v>6624625</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9704,7 +9690,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9714,7 +9700,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Hackspår i gammalt träd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9723,29 +9714,38 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Gammal barrskog, partier med sumpskog, död ved</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>116057023</v>
+        <v>121290063</v>
       </c>
       <c r="B72" t="n">
-        <v>97659</v>
+        <v>98110</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9794,14 +9794,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563515</v>
+        <v>563415</v>
       </c>
       <c r="R72" t="n">
-        <v>6624652</v>
+        <v>6624521</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9826,24 +9826,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>U-Sur-0799</t>
+        </is>
+      </c>
       <c r="Y72" t="inlineStr">
         <is>
           <t>2024-04-17</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-04-17</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9859,74 +9859,66 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>116057309</v>
+        <v>122485434</v>
       </c>
       <c r="B73" t="n">
-        <v>57281</v>
+        <v>98365</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>563448</v>
+        <v>563429</v>
       </c>
       <c r="R73" t="n">
-        <v>6624536</v>
+        <v>6624616</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9953,22 +9945,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9979,30 +9961,39 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>116057771</v>
+        <v>122485432</v>
       </c>
       <c r="B74" t="n">
-        <v>57281</v>
+        <v>95911</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10011,49 +10002,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>563542</v>
+        <v>563279</v>
       </c>
       <c r="R74" t="n">
-        <v>6624450</v>
+        <v>6624575</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10077,22 +10056,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10103,77 +10072,83 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Liggande murken tallstam</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>116041402</v>
+        <v>122485433</v>
       </c>
       <c r="B75" t="n">
-        <v>57281</v>
+        <v>105471</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>563537</v>
+        <v>563393</v>
       </c>
       <c r="R75" t="n">
-        <v>6624625</v>
+        <v>6624475</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10197,27 +10172,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Hackspår i gammalt träd</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10229,35 +10189,34 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Gammal barrskog, partier med sumpskog, död ved</t>
+          <t>Äldre granblandad tallskog</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121291351</v>
+        <v>122485428</v>
       </c>
       <c r="B76" t="n">
-        <v>98110</v>
+        <v>90724</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10266,57 +10225,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 3 (knärot), Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563447</v>
+        <v>563459</v>
       </c>
       <c r="R76" t="n">
-        <v>6624479</v>
+        <v>6624572</v>
       </c>
       <c r="S76" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10338,24 +10281,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>U-Sur-0533</t>
-        </is>
-      </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>1907992(5) 2 m2, 11/984(5) 4 m2, 207/999(5) 5 m2, 207/26001(5) 4 m2, 214/26007(5) 2 m2, 200/226009(5) 1 m2, 214/26000(5) 2 m2</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10364,33 +10297,37 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121290063</v>
+        <v>122485424</v>
       </c>
       <c r="B77" t="n">
-        <v>98110</v>
+        <v>90952</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10399,57 +10336,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563415</v>
+        <v>563482</v>
       </c>
       <c r="R77" t="n">
-        <v>6624521</v>
+        <v>6624454</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10471,24 +10392,14 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>U-Sur-0799</t>
-        </is>
-      </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>foto OK</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10497,33 +10408,42 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122485434</v>
+        <v>123093272</v>
       </c>
       <c r="B78" t="n">
-        <v>98365</v>
+        <v>90990</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10532,41 +10452,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkraken S, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563429</v>
+        <v>563490</v>
       </c>
       <c r="R78" t="n">
-        <v>6624616</v>
+        <v>6624468</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10590,12 +10513,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10604,37 +10527,39 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122485432</v>
+        <v>123093244</v>
       </c>
       <c r="B79" t="n">
-        <v>95911</v>
+        <v>90990</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10647,37 +10572,40 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkraken S, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563279</v>
+        <v>563463</v>
       </c>
       <c r="R79" t="n">
-        <v>6624575</v>
+        <v>6624447</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10701,12 +10629,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10715,42 +10643,39 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Liggande murken tallstam</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122485433</v>
+        <v>123093296</v>
       </c>
       <c r="B80" t="n">
-        <v>105471</v>
+        <v>90990</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10759,41 +10684,44 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkraken S, Vstm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563393</v>
+        <v>563612</v>
       </c>
       <c r="R80" t="n">
-        <v>6624475</v>
+        <v>6624481</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10817,12 +10745,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10831,610 +10764,32 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>122485428</v>
-      </c>
-      <c r="B81" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Syd Fiskkraken, Vstm</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>563459</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6624572</v>
-      </c>
-      <c r="S81" t="n">
-        <v>25</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
-        </is>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Aivars Dunskis</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>122485424</v>
-      </c>
-      <c r="B82" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Syd Fiskkraken, Vstm</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>563482</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6624454</v>
-      </c>
-      <c r="S82" t="n">
-        <v>25</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Barrblandskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
-        </is>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Aivars Dunskis</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>123093296</v>
-      </c>
-      <c r="B83" t="n">
-        <v>90988</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Fiskkraken S, Vstm</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>563612</v>
-      </c>
-      <c r="R83" t="n">
-        <v>6624481</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lutande gran.</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>123093272</v>
-      </c>
-      <c r="B84" t="n">
-        <v>90988</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Fiskkraken S, Vstm</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>563490</v>
-      </c>
-      <c r="R84" t="n">
-        <v>6624468</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="inlineStr"/>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>123093244</v>
-      </c>
-      <c r="B85" t="n">
-        <v>90988</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Fiskkraken S, Vstm</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>563463</v>
-      </c>
-      <c r="R85" t="n">
-        <v>6624447</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF85" t="inlineStr"/>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10791,6 +10791,600 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128452150</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98393</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>563513</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6624449</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128437425</v>
+      </c>
+      <c r="B82" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>563490</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6624458</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128437458</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>563490</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6624458</v>
+      </c>
+      <c r="S83" t="n">
+        <v>30</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128437301</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98393</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>563490</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6624458</v>
+      </c>
+      <c r="S84" t="n">
+        <v>4</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128437337</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91358</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>563490</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6624458</v>
+      </c>
+      <c r="S85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10796,7 +10796,7 @@
         <v>128452150</v>
       </c>
       <c r="B81" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>128437301</v>
       </c>
       <c r="B84" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>128437337</v>
       </c>
       <c r="B85" t="n">
-        <v>91358</v>
+        <v>91360</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10796,7 +10796,7 @@
         <v>128452150</v>
       </c>
       <c r="B81" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>128437458</v>
       </c>
       <c r="B83" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>128437301</v>
       </c>
       <c r="B84" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>128437337</v>
       </c>
       <c r="B85" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10796,7 +10796,7 @@
         <v>128452150</v>
       </c>
       <c r="B81" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>128437458</v>
       </c>
       <c r="B83" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>128437301</v>
       </c>
       <c r="B84" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>128437337</v>
       </c>
       <c r="B85" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10796,7 +10796,7 @@
         <v>128452150</v>
       </c>
       <c r="B81" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>128437301</v>
       </c>
       <c r="B84" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>128437337</v>
       </c>
       <c r="B85" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10796,7 +10796,7 @@
         <v>128452150</v>
       </c>
       <c r="B81" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>128437301</v>
       </c>
       <c r="B84" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10796,7 +10796,7 @@
         <v>128452150</v>
       </c>
       <c r="B81" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>128437301</v>
       </c>
       <c r="B84" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>128437337</v>
       </c>
       <c r="B85" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -10796,7 +10796,7 @@
         <v>128452150</v>
       </c>
       <c r="B81" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>128437458</v>
       </c>
       <c r="B83" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>128437301</v>
       </c>
       <c r="B84" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>128437337</v>
       </c>
       <c r="B85" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11264,7 +11264,7 @@
         <v>128437458</v>
       </c>
       <c r="B85" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -11264,7 +11264,7 @@
         <v>128437458</v>
       </c>
       <c r="B85" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108248677</v>
+        <v>122485432</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563543.9950642779</v>
+        <v>563279</v>
       </c>
       <c r="R2" t="n">
-        <v>6624579.101406045</v>
+        <v>6624575</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,88 +754,80 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Liggande murken tallstam</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108724061</v>
+        <v>122485429</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563506.9327795741</v>
+        <v>563577</v>
       </c>
       <c r="R3" t="n">
-        <v>6624502.363565752</v>
+        <v>6624654</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,88 +865,80 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Basen av torrtall</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108723657</v>
+        <v>122485424</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563321.9257743037</v>
+        <v>563482</v>
       </c>
       <c r="R4" t="n">
-        <v>6624545.080462361</v>
+        <v>6624454</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,88 +976,83 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog, fuktsänka</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108723685</v>
+        <v>123093244</v>
       </c>
       <c r="B5" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkraken S, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563338.5817877789</v>
+        <v>563463</v>
       </c>
       <c r="R5" t="n">
-        <v>6624545.363541753</v>
+        <v>6624447</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1148,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,77 +1094,76 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108724045</v>
+        <v>123093272</v>
       </c>
       <c r="B6" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkraken S, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563440.2650425377</v>
+        <v>563490</v>
       </c>
       <c r="R6" t="n">
-        <v>6624503.748048831</v>
+        <v>6624468</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,27 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,77 +1205,76 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108723183</v>
+        <v>123093296</v>
       </c>
       <c r="B7" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkraken S, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563410.8548510254</v>
+        <v>563612</v>
       </c>
       <c r="R7" t="n">
-        <v>6624689.225368067</v>
+        <v>6624481</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,27 +1298,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På relativt klen gran</t>
+          <t>Lutande gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,84 +1321,73 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109201851</v>
+        <v>128437337</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563520.8546479825</v>
+        <v>563490</v>
       </c>
       <c r="R8" t="n">
-        <v>6624455.726856424</v>
+        <v>6624458</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1531,22 +1411,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,88 +1440,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111353154</v>
+        <v>122485428</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skallmossarna SO, Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563523.971029468</v>
+        <v>563459</v>
       </c>
       <c r="R9" t="n">
-        <v>6624421.002114353</v>
+        <v>6624572</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1660,22 +1523,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1684,61 +1537,59 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111356627</v>
+        <v>116057445</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1748,29 +1599,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skallmossarna, SO, 1 (knärot), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563488.6664139299</v>
+        <v>563447</v>
       </c>
       <c r="R10" t="n">
-        <v>6624389.150503646</v>
+        <v>6624478</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1792,29 +1638,29 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>U-Sur-0531</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Invid tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1827,93 +1673,71 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111353098</v>
+        <v>115440622</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skallmossarna SO, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563447.2555399563</v>
+        <v>563578</v>
       </c>
       <c r="R11" t="n">
-        <v>6624478.66609251</v>
+        <v>6624436</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1937,22 +1761,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosök på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1961,90 +1790,76 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog</t>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111353050</v>
+        <v>116041402</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skallmossarna SO, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm, Skallmosseskogen, Ramäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563407.5613832783</v>
+        <v>563537</v>
       </c>
       <c r="R12" t="n">
-        <v>6624467.405989128</v>
+        <v>6624625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,22 +1886,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår i gammalt träd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2095,61 +1915,60 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Gammal barrskog, partier med sumpskog, död ved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111353127</v>
+        <v>116057309</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2157,31 +1976,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skallmossarna SO, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563506.2190936843</v>
+        <v>563448</v>
       </c>
       <c r="R13" t="n">
-        <v>6624425.739831987</v>
+        <v>6624536</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2205,22 +2020,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,61 +2044,50 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115332800</v>
+        <v>116057771</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2291,32 +2095,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563546</v>
+        <v>563542</v>
       </c>
       <c r="R14" t="n">
-        <v>6624433</v>
+        <v>6624450</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2343,12 +2139,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2357,92 +2163,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115332530</v>
+        <v>128437425</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563512</v>
+        <v>563490</v>
       </c>
       <c r="R15" t="n">
-        <v>6624412</v>
+        <v>6624458</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2466,22 +2246,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2490,7 +2270,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2509,73 +2288,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115331339</v>
+        <v>108723183</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563492</v>
+        <v>563411</v>
       </c>
       <c r="R16" t="n">
-        <v>6624444</v>
+        <v>6624689</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2599,22 +2362,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På relativt klen gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2630,78 +2398,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115452935</v>
+        <v>108724045</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fiskkrkenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>563614</v>
+        <v>563440</v>
       </c>
       <c r="R17" t="n">
-        <v>6624509</v>
+        <v>6624504</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2728,22 +2484,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2764,76 +2525,69 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115452717</v>
+        <v>128437458</v>
       </c>
       <c r="B18" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>563606</v>
+        <v>563490</v>
       </c>
       <c r="R18" t="n">
-        <v>6624632</v>
+        <v>6624458</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2857,22 +2611,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2881,56 +2635,55 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115452851</v>
+        <v>128437301</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2940,29 +2693,27 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>563600</v>
+        <v>563490</v>
       </c>
       <c r="R19" t="n">
-        <v>6624606</v>
+        <v>6624458</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2986,22 +2737,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3010,34 +2761,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115452883</v>
+        <v>128452150</v>
       </c>
       <c r="B20" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3045,26 +2795,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3074,21 +2824,25 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>563617</v>
+        <v>563513</v>
       </c>
       <c r="R20" t="n">
-        <v>6624585</v>
+        <v>6624449</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3115,22 +2869,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3143,30 +2887,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115452914</v>
+        <v>108248677</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3193,7 +2937,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3214,10 +2958,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>563623</v>
+        <v>563544</v>
       </c>
       <c r="R21" t="n">
-        <v>6624566</v>
+        <v>6624579</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3244,7 +2988,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3254,12 +2998,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3280,65 +3024,68 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115440622</v>
+        <v>108723657</v>
       </c>
       <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563578</v>
+        <v>563322</v>
       </c>
       <c r="R22" t="n">
-        <v>6624436</v>
+        <v>6624545</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3365,27 +3112,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosök på gran</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3394,89 +3136,83 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115602430</v>
+        <v>108724061</v>
       </c>
       <c r="B23" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>av Fiskkraken, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563476</v>
+        <v>563507</v>
       </c>
       <c r="R23" t="n">
-        <v>6624515</v>
+        <v>6624502</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3500,12 +3236,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3521,27 +3267,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116057705</v>
+        <v>109201851</v>
       </c>
       <c r="B24" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3568,7 +3309,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3589,10 +3330,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>563515</v>
+        <v>563521</v>
       </c>
       <c r="R24" t="n">
-        <v>6624433</v>
+        <v>6624456</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3619,7 +3360,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3629,12 +3370,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3655,22 +3396,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116057717</v>
+        <v>111353050</v>
       </c>
       <c r="B25" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3697,7 +3433,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3707,24 +3443,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmossarna SO, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>563550</v>
+        <v>563408</v>
       </c>
       <c r="R25" t="n">
-        <v>6624428</v>
+        <v>6624467</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3748,22 +3484,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3776,30 +3502,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116057037</v>
+        <v>111353098</v>
       </c>
       <c r="B26" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3836,24 +3562,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmossarna SO, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563502</v>
+        <v>563447</v>
       </c>
       <c r="R26" t="n">
-        <v>6624626</v>
+        <v>6624479</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3877,22 +3603,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3905,52 +3621,52 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116057566</v>
+        <v>111353127</v>
       </c>
       <c r="B27" t="n">
-        <v>104746</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3965,24 +3681,24 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmossarna SO, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>563424</v>
+        <v>563506</v>
       </c>
       <c r="R27" t="n">
-        <v>6624463</v>
+        <v>6624425</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4006,22 +3722,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4034,30 +3740,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116057720</v>
+        <v>111353154</v>
       </c>
       <c r="B28" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4084,7 +3790,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4094,24 +3800,24 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmossarna SO, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>563561</v>
+        <v>563524</v>
       </c>
       <c r="R28" t="n">
-        <v>6624427</v>
+        <v>6624421</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4135,22 +3841,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4163,57 +3859,57 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116042256</v>
+        <v>111353172</v>
       </c>
       <c r="B29" t="n">
-        <v>96622</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4221,26 +3917,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Skallmossarna SO, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563537</v>
+        <v>563488</v>
       </c>
       <c r="R29" t="n">
-        <v>6624625</v>
+        <v>6624389</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4264,22 +3960,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4292,35 +3978,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116057150</v>
+        <v>111356627</v>
       </c>
       <c r="B30" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4347,7 +4028,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4357,24 +4038,24 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmossarna, SO, 1 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>563458</v>
+        <v>563489</v>
       </c>
       <c r="R30" t="n">
-        <v>6624624</v>
+        <v>6624389</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4396,24 +4077,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>U-Sur-0531</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4426,30 +4102,34 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116057372</v>
+        <v>115331339</v>
       </c>
       <c r="B31" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4476,7 +4156,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4490,20 +4170,24 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563441</v>
+        <v>563492</v>
       </c>
       <c r="R31" t="n">
-        <v>6624477</v>
+        <v>6624444</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4527,22 +4211,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4558,27 +4242,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116057204</v>
+        <v>115332530</v>
       </c>
       <c r="B32" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4605,7 +4284,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4619,17 +4298,21 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563459</v>
+        <v>563512</v>
       </c>
       <c r="R32" t="n">
-        <v>6624536</v>
+        <v>6624412</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4656,22 +4339,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4687,27 +4370,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116057108</v>
+        <v>115332800</v>
       </c>
       <c r="B33" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4748,17 +4426,21 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>563438</v>
+        <v>563546</v>
       </c>
       <c r="R33" t="n">
-        <v>6624576</v>
+        <v>6624433</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4785,22 +4467,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4816,71 +4488,73 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116042390</v>
+        <v>115446726</v>
       </c>
       <c r="B34" t="n">
-        <v>96622</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>563417</v>
+        <v>563608</v>
       </c>
       <c r="R34" t="n">
-        <v>6624534</v>
+        <v>6624675</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4907,22 +4581,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4931,38 +4605,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Otto Lindgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116057189</v>
+        <v>115446801</v>
       </c>
       <c r="B35" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4989,7 +4654,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5010,10 +4675,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>563435</v>
+        <v>563594</v>
       </c>
       <c r="R35" t="n">
-        <v>6624509</v>
+        <v>6624669</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5040,22 +4705,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5076,22 +4741,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Otto Lindgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116057331</v>
+        <v>115452381</v>
       </c>
       <c r="B36" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5139,10 +4799,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563434</v>
+        <v>563614</v>
       </c>
       <c r="R36" t="n">
-        <v>6624484</v>
+        <v>6624671</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5169,22 +4829,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5205,22 +4865,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116057635</v>
+        <v>115452601</v>
       </c>
       <c r="B37" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5268,10 +4923,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>563401</v>
+        <v>563607</v>
       </c>
       <c r="R37" t="n">
-        <v>6624447</v>
+        <v>6624658</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5298,22 +4953,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5334,44 +4989,39 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116057445</v>
+        <v>115452644</v>
       </c>
       <c r="B38" t="n">
-        <v>90744</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5381,10 +5031,15 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5392,10 +5047,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>563447</v>
+        <v>563601</v>
       </c>
       <c r="R38" t="n">
-        <v>6624478</v>
+        <v>6624655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5422,27 +5077,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Invid tall</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5463,22 +5113,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>116057251</v>
+        <v>115452851</v>
       </c>
       <c r="B39" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5505,7 +5150,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5526,10 +5171,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563447</v>
+        <v>563600</v>
       </c>
       <c r="R39" t="n">
-        <v>6624476</v>
+        <v>6624606</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5556,22 +5201,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5592,22 +5237,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>116042524</v>
+        <v>115452914</v>
       </c>
       <c r="B40" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5634,7 +5274,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5648,24 +5288,20 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563415</v>
+        <v>563623</v>
       </c>
       <c r="R40" t="n">
-        <v>6624523</v>
+        <v>6624566</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5689,22 +5325,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5717,39 +5353,25 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>116057713</v>
+        <v>115452935</v>
       </c>
       <c r="B41" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5793,14 +5415,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Fiskkrkenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563533</v>
+        <v>563614</v>
       </c>
       <c r="R41" t="n">
-        <v>6624432</v>
+        <v>6624509</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5827,22 +5449,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5863,22 +5485,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>116057764</v>
+        <v>116042524</v>
       </c>
       <c r="B42" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5905,7 +5522,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5919,20 +5536,24 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+          <t>Skallmosseskogen, Ramäs, Vstm, Skallmosseskogen, Ramäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563560</v>
+        <v>563415</v>
       </c>
       <c r="R42" t="n">
-        <v>6624441</v>
+        <v>6624523</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5961,7 +5582,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5971,7 +5592,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5984,30 +5605,34 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Bengt Eriksson, Pia Hagfors, Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>116057179</v>
+        <v>116057008</v>
       </c>
       <c r="B43" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6055,10 +5680,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>563430</v>
+        <v>563523</v>
       </c>
       <c r="R43" t="n">
-        <v>6624513</v>
+        <v>6624636</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6128,15 +5753,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116057008</v>
+        <v>116057016</v>
       </c>
       <c r="B44" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6163,7 +5783,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6184,10 +5804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>563523</v>
+        <v>563522</v>
       </c>
       <c r="R44" t="n">
-        <v>6624636</v>
+        <v>6624629</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6257,15 +5877,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116057342</v>
+        <v>116057023</v>
       </c>
       <c r="B45" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6313,10 +5928,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563447</v>
+        <v>563515</v>
       </c>
       <c r="R45" t="n">
-        <v>6624483</v>
+        <v>6624652</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6386,15 +6001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>116057525</v>
+        <v>116057037</v>
       </c>
       <c r="B46" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6421,7 +6031,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6442,10 +6052,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563441</v>
+        <v>563502</v>
       </c>
       <c r="R46" t="n">
-        <v>6624475</v>
+        <v>6624626</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6515,15 +6125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>116057624</v>
+        <v>116057108</v>
       </c>
       <c r="B47" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6550,7 +6155,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6571,10 +6176,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>563400</v>
+        <v>563438</v>
       </c>
       <c r="R47" t="n">
-        <v>6624449</v>
+        <v>6624576</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6644,15 +6249,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116057643</v>
+        <v>116057150</v>
       </c>
       <c r="B48" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6679,7 +6279,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6700,10 +6300,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>563411</v>
+        <v>563458</v>
       </c>
       <c r="R48" t="n">
-        <v>6624447</v>
+        <v>6624624</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6773,15 +6373,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116057699</v>
+        <v>116057176</v>
       </c>
       <c r="B49" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6808,7 +6403,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6829,10 +6424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563505</v>
+        <v>563423</v>
       </c>
       <c r="R49" t="n">
-        <v>6624422</v>
+        <v>6624532</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6895,22 +6490,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>116057176</v>
+        <v>116057179</v>
       </c>
       <c r="B50" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6937,7 +6527,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6958,10 +6548,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>563423</v>
+        <v>563430</v>
       </c>
       <c r="R50" t="n">
-        <v>6624532</v>
+        <v>6624513</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -7031,15 +6621,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116057677</v>
+        <v>116057189</v>
       </c>
       <c r="B51" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7066,7 +6651,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7087,10 +6672,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563473</v>
+        <v>563435</v>
       </c>
       <c r="R51" t="n">
-        <v>6624426</v>
+        <v>6624509</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -7153,22 +6738,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116057798</v>
+        <v>116057204</v>
       </c>
       <c r="B52" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7195,7 +6775,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7216,10 +6796,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563598</v>
+        <v>563459</v>
       </c>
       <c r="R52" t="n">
-        <v>6624441</v>
+        <v>6624536</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -7289,15 +6869,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116057631</v>
+        <v>116057251</v>
       </c>
       <c r="B53" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7324,7 +6899,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7345,10 +6920,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563404</v>
+        <v>563447</v>
       </c>
       <c r="R53" t="n">
-        <v>6624452</v>
+        <v>6624476</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7418,15 +6993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116057793</v>
+        <v>116057331</v>
       </c>
       <c r="B54" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7453,7 +7023,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7474,10 +7044,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>563592</v>
+        <v>563434</v>
       </c>
       <c r="R54" t="n">
-        <v>6624431</v>
+        <v>6624484</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7547,15 +7117,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116057540</v>
+        <v>116057342</v>
       </c>
       <c r="B55" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7582,7 +7147,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7603,10 +7168,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>563445</v>
+        <v>563447</v>
       </c>
       <c r="R55" t="n">
-        <v>6624460</v>
+        <v>6624483</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7676,15 +7241,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116057654</v>
+        <v>116057372</v>
       </c>
       <c r="B56" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7711,7 +7271,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7732,10 +7292,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>563458</v>
+        <v>563441</v>
       </c>
       <c r="R56" t="n">
-        <v>6624424</v>
+        <v>6624477</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7798,22 +7358,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116057016</v>
+        <v>116057525</v>
       </c>
       <c r="B57" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7840,7 +7395,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7861,10 +7416,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>563522</v>
+        <v>563441</v>
       </c>
       <c r="R57" t="n">
-        <v>6624629</v>
+        <v>6624475</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7934,42 +7489,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>116057638</v>
+        <v>116057540</v>
       </c>
       <c r="B58" t="n">
-        <v>104746</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7990,10 +7540,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>563401</v>
+        <v>563445</v>
       </c>
       <c r="R58" t="n">
-        <v>6624447</v>
+        <v>6624460</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -8063,15 +7613,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>116057709</v>
+        <v>116057553</v>
       </c>
       <c r="B59" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8098,7 +7643,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8119,10 +7664,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>563523</v>
+        <v>563424</v>
       </c>
       <c r="R59" t="n">
-        <v>6624427</v>
+        <v>6624468</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -8185,49 +7730,44 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>116042323</v>
+        <v>116057617</v>
       </c>
       <c r="B60" t="n">
-        <v>96619</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8235,22 +7775,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>563420</v>
+        <v>563413</v>
       </c>
       <c r="R60" t="n">
-        <v>6624535</v>
+        <v>6624452</v>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8279,7 +7823,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8289,7 +7833,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8302,57 +7846,47 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>116040948</v>
+        <v>116057624</v>
       </c>
       <c r="B61" t="n">
-        <v>96619</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8365,26 +7899,26 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>563537</v>
+        <v>563400</v>
       </c>
       <c r="R61" t="n">
-        <v>6624625</v>
+        <v>6624449</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8413,7 +7947,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8423,7 +7957,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8436,35 +7970,25 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>116057723</v>
+        <v>116057631</v>
       </c>
       <c r="B62" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8491,7 +8015,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8512,10 +8036,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563549</v>
+        <v>563404</v>
       </c>
       <c r="R62" t="n">
-        <v>6624415</v>
+        <v>6624452</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8578,49 +8102,44 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>116057573</v>
+        <v>116057635</v>
       </c>
       <c r="B63" t="n">
-        <v>104746</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8641,10 +8160,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563415</v>
+        <v>563401</v>
       </c>
       <c r="R63" t="n">
-        <v>6624457</v>
+        <v>6624447</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8714,15 +8233,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>116057689</v>
+        <v>116057643</v>
       </c>
       <c r="B64" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8770,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>563486</v>
+        <v>563411</v>
       </c>
       <c r="R64" t="n">
-        <v>6624438</v>
+        <v>6624447</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8836,22 +8350,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>116057734</v>
+        <v>116057654</v>
       </c>
       <c r="B65" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8878,7 +8387,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8899,10 +8408,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563562</v>
+        <v>563458</v>
       </c>
       <c r="R65" t="n">
-        <v>6624421</v>
+        <v>6624424</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8965,22 +8474,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Eriksson, Seppo Ormiskangas, Pia Hagfors, Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>116057553</v>
+        <v>116057677</v>
       </c>
       <c r="B66" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9028,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563424</v>
+        <v>563473</v>
       </c>
       <c r="R66" t="n">
-        <v>6624468</v>
+        <v>6624426</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -9101,15 +8605,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>116057617</v>
+        <v>116057689</v>
       </c>
       <c r="B67" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9136,7 +8635,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9157,10 +8656,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563413</v>
+        <v>563486</v>
       </c>
       <c r="R67" t="n">
-        <v>6624452</v>
+        <v>6624438</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -9230,15 +8729,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>116057023</v>
+        <v>116057699</v>
       </c>
       <c r="B68" t="n">
-        <v>97659</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9265,7 +8759,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9286,10 +8780,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>563515</v>
+        <v>563505</v>
       </c>
       <c r="R68" t="n">
-        <v>6624652</v>
+        <v>6624422</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9359,51 +8853,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>116057309</v>
+        <v>116057705</v>
       </c>
       <c r="B69" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9411,13 +8904,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563448</v>
+        <v>563515</v>
       </c>
       <c r="R69" t="n">
-        <v>6624536</v>
+        <v>6624433</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9465,6 +8958,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9483,51 +8977,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>116057771</v>
+        <v>116057709</v>
       </c>
       <c r="B70" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9535,10 +9028,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563542</v>
+        <v>563523</v>
       </c>
       <c r="R70" t="n">
-        <v>6624450</v>
+        <v>6624427</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9589,6 +9082,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9607,61 +9101,64 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>116041402</v>
+        <v>116057713</v>
       </c>
       <c r="B71" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Ramäs, Vstm (Skallmosseskogen, Ramäs, Vstm), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>563537</v>
+        <v>563533</v>
       </c>
       <c r="R71" t="n">
-        <v>6624625</v>
+        <v>6624432</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9690,7 +9187,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9700,12 +9197,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Hackspår i gammalt träd</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9714,43 +9206,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Gammal barrskog, partier med sumpskog, död ved</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121290063</v>
+        <v>116057717</v>
       </c>
       <c r="B72" t="n">
-        <v>98110</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9777,7 +9255,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9794,14 +9272,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skallmosseskogen (E) (knärot), Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563415</v>
+        <v>563550</v>
       </c>
       <c r="R72" t="n">
-        <v>6624521</v>
+        <v>6624428</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9826,24 +9304,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>U-Sur-0799</t>
-        </is>
-      </c>
       <c r="Y72" t="inlineStr">
         <is>
           <t>2024-04-17</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-04-17</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>foto OK</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9859,31 +9337,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122485434</v>
+        <v>116057720</v>
       </c>
       <c r="B73" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9908,20 +9377,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>563429</v>
+        <v>563561</v>
       </c>
       <c r="R73" t="n">
-        <v>6624616</v>
+        <v>6624427</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9945,12 +9430,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9959,80 +9454,83 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Äldre granblandad tallskog, blåbärsris</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122485432</v>
+        <v>116057723</v>
       </c>
       <c r="B74" t="n">
-        <v>95911</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>563279</v>
+        <v>563549</v>
       </c>
       <c r="R74" t="n">
-        <v>6624575</v>
+        <v>6624415</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10056,12 +9554,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10070,85 +9578,83 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Äldre granblandad tallskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Liggande murken tallstam</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122485433</v>
+        <v>116057734</v>
       </c>
       <c r="B75" t="n">
-        <v>105471</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>563393</v>
+        <v>563562</v>
       </c>
       <c r="R75" t="n">
-        <v>6624475</v>
+        <v>6624421</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10172,12 +9678,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10186,80 +9702,83 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122485428</v>
+        <v>116057764</v>
       </c>
       <c r="B76" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563459</v>
+        <v>563560</v>
       </c>
       <c r="R76" t="n">
-        <v>6624572</v>
+        <v>6624441</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10283,12 +9802,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10297,80 +9826,83 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Äldre granblandad tallskog, örtstråk fuktsänka</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122485424</v>
+        <v>116057793</v>
       </c>
       <c r="B77" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Syd Fiskkraken, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>563482</v>
+        <v>563592</v>
       </c>
       <c r="R77" t="n">
-        <v>6624454</v>
+        <v>6624431</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10394,12 +9926,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10408,88 +9950,83 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Barrblandskog, fuktsänka</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123093272</v>
+        <v>116057798</v>
       </c>
       <c r="B78" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fiskkraken S, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>563490</v>
+        <v>563598</v>
       </c>
       <c r="R78" t="n">
-        <v>6624468</v>
+        <v>6624441</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10513,12 +10050,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10531,81 +10078,79 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123093244</v>
+        <v>116057812</v>
       </c>
       <c r="B79" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fiskkraken S, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>563463</v>
+        <v>563571</v>
       </c>
       <c r="R79" t="n">
-        <v>6624447</v>
+        <v>6624668</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10629,12 +10174,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10647,81 +10202,79 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123093296</v>
+        <v>121290063</v>
       </c>
       <c r="B80" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fiskkraken S, Vstm</t>
+          <t>Skallmosseskogen (E) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>563612</v>
+        <v>563415</v>
       </c>
       <c r="R80" t="n">
-        <v>6624481</v>
+        <v>6624521</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10743,19 +10296,24 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>U-Sur-0799</t>
+        </is>
+      </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Lutande gran.</t>
+          <t>foto OK</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10768,57 +10326,51 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128452150</v>
+        <v>121291226</v>
       </c>
       <c r="B81" t="n">
-        <v>98562</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10828,30 +10380,26 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fiskkrakenskogen, Ramnäs, Vstm</t>
+          <t>Fiskrakenskogen (9) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563513</v>
+        <v>563351</v>
       </c>
       <c r="R81" t="n">
-        <v>6624449</v>
+        <v>6624447</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10876,14 +10424,19 @@
           <t>Ramnäs</t>
         </is>
       </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>U-Sur-0803</t>
+        </is>
+      </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10896,68 +10449,67 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128437425</v>
+        <v>122485434</v>
       </c>
       <c r="B82" t="n">
-        <v>4773</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Syd Fiskkraken, Vstm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>563490</v>
+        <v>563429</v>
       </c>
       <c r="R82" t="n">
-        <v>6624458</v>
+        <v>6624616</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10981,22 +10533,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11007,26 +10549,35 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog, blåbärsris</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128437301</v>
+        <v>115446837</v>
       </c>
       <c r="B83" t="n">
-        <v>98562</v>
+        <v>106244</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11034,51 +10585,53 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219790</v>
+        <v>221144</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>563490</v>
+        <v>563600</v>
       </c>
       <c r="R83" t="n">
-        <v>6624458</v>
+        <v>6624673</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11102,22 +10655,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11126,71 +10679,83 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Otto Lindgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128437337</v>
+        <v>115446865</v>
       </c>
       <c r="B84" t="n">
-        <v>91515</v>
+        <v>106244</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>563490</v>
+        <v>563607</v>
       </c>
       <c r="R84" t="n">
-        <v>6624458</v>
+        <v>6624671</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11214,27 +10779,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11243,80 +10803,83 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Otto Lindgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128437458</v>
+        <v>115452717</v>
       </c>
       <c r="B85" t="n">
-        <v>57887</v>
+        <v>106244</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skallmosseskogen, Fiskkraken, Ramnäs, Skallmosseskogen, Fiskkraken, Ramnäs, Vstm</t>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563490</v>
+        <v>563606</v>
       </c>
       <c r="R85" t="n">
-        <v>6624458</v>
+        <v>6624632</v>
       </c>
       <c r="S85" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11340,22 +10903,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11364,26 +10927,1363 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>115452883</v>
+      </c>
+      <c r="B86" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>563617</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6624585</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Otto Lindgren, Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>115602430</v>
+      </c>
+      <c r="B87" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>av Fiskkraken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>563476</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6624515</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>116057566</v>
+      </c>
+      <c r="B88" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>563424</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6624463</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>116057573</v>
+      </c>
+      <c r="B89" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>563415</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6624457</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>116057638</v>
+      </c>
+      <c r="B90" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>563401</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6624447</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>122485433</v>
+      </c>
+      <c r="B91" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Syd Fiskkraken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>563393</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6624475</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>108723685</v>
+      </c>
+      <c r="B92" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Fiskkrakenskogen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>563339</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6624545</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>116040948</v>
+      </c>
+      <c r="B93" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Ramäs, Vstm, Skallmosseskogen, Ramäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>563537</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6624625</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
+      <c r="AX93" t="inlineStr">
         <is>
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY85" t="inlineStr"/>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>116042323</v>
+      </c>
+      <c r="B94" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Ramäs, Vstm, Skallmosseskogen, Ramäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>563420</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6624535</v>
+      </c>
+      <c r="S94" t="n">
+        <v>2</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>116042256</v>
+      </c>
+      <c r="B95" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Ramäs, Vstm, Skallmosseskogen, Ramäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>563537</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6624625</v>
+      </c>
+      <c r="S95" t="n">
+        <v>2</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>116042390</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Skallmosseskogen, Ramäs, Vstm, Skallmosseskogen, Ramäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>563417</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6624534</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65022-2023 artfynd.xlsx
+++ b/artfynd/A 65022-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485432</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485429</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485424</t>
         </is>
       </c>
     </row>
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123093244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123093272</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123093296</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437337</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485428</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057445</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1810,6 +1860,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115440622</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1940,6 +1995,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116041402</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2059,6 +2119,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057309</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2178,6 +2243,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057771</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2285,6 +2355,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437425</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2407,6 +2482,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108723183</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2529,6 +2609,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108724045</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2655,6 +2740,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437458</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2781,6 +2871,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437301</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2904,6 +2999,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128452150</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3028,6 +3128,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108248677</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3152,6 +3257,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108723657</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3276,6 +3386,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108724061</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3400,6 +3515,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109201851</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3519,6 +3639,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111353050</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3638,6 +3763,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111353098</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3757,6 +3887,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111353127</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3876,6 +4011,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111353154</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3995,6 +4135,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111353172</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4123,6 +4268,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4251,6 +4401,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115331339</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4379,6 +4534,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115332530</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4497,6 +4657,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115332800</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4621,6 +4786,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115446726</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4745,6 +4915,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115446801</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4869,6 +5044,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452381</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4993,6 +5173,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452601</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5117,6 +5302,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452644</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5241,6 +5431,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452851</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5365,6 +5560,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452914</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5489,6 +5689,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452935</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5626,6 +5831,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116042524</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5750,6 +5960,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057008</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5874,6 +6089,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057016</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5998,6 +6218,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057023</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6122,6 +6347,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057037</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6246,6 +6476,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057108</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6370,6 +6605,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057150</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6494,6 +6734,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057176</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6618,6 +6863,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057179</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6742,6 +6992,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057189</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6866,6 +7121,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057204</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6990,6 +7250,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057251</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7114,6 +7379,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057331</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7238,6 +7508,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057342</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7362,6 +7637,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057372</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7486,6 +7766,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057525</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7610,6 +7895,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057540</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7734,6 +8024,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057553</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7858,6 +8153,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057617</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7982,6 +8282,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057624</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8106,6 +8411,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057631</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8230,6 +8540,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057635</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8354,6 +8669,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057643</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8478,6 +8798,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057654</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8602,6 +8927,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057677</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8726,6 +9056,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057689</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8850,6 +9185,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057699</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8974,6 +9314,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057705</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9098,6 +9443,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057709</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9222,6 +9572,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057713</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9346,6 +9701,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057717</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9470,6 +9830,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057720</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9594,6 +9959,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057723</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9718,6 +10088,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057734</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9842,6 +10217,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057764</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9966,6 +10346,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057793</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10090,6 +10475,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057798</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10214,6 +10604,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057812</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10342,6 +10737,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121290063</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10465,6 +10865,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291226</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10571,6 +10976,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485434</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10695,6 +11105,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115446837</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10819,6 +11234,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115446865</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10943,6 +11363,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452717</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11067,6 +11492,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452883</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11178,6 +11608,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115602430</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11302,6 +11737,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057566</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11426,6 +11866,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057573</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11550,6 +11995,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116057638</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11656,6 +12106,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485433</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11780,6 +12235,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108723685</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11909,6 +12369,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116040948</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12034,6 +12499,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116042323</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12163,6 +12633,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116042256</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12284,8 +12759,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116042390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>